--- a/artfynd/A 44865-2025 artfynd.xlsx
+++ b/artfynd/A 44865-2025 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>99957121</v>
+        <v>99957101</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,7 +705,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>15</t>
+          <t>30</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -727,10 +722,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>587314.399367233</v>
+        <v>587298</v>
       </c>
       <c r="R2" t="n">
-        <v>6385211.451872115</v>
+        <v>6385220</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -800,15 +795,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>99957101</v>
+        <v>99957121</v>
       </c>
       <c r="B3" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -835,7 +825,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -852,10 +842,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>587298.0990046011</v>
+        <v>587314</v>
       </c>
       <c r="R3" t="n">
-        <v>6385220.213213564</v>
+        <v>6385211</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
